--- a/output/pdf_financials_xlsx/MOOD.xlsx
+++ b/output/pdf_financials_xlsx/MOOD.xlsx
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.385065</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.462602</v>
       </c>
     </row>
     <row r="93">
@@ -3808,7 +3808,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MOOD.xlsx
+++ b/output/pdf_financials_xlsx/MOOD.xlsx
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02929</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023818</v>
       </c>
     </row>
     <row r="13">
@@ -1008,10 +1008,10 @@
         <v>-1.781544</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.339848</v>
+        <v>-0.369138</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.339848</v>
+        <v>-0.363666</v>
       </c>
     </row>
     <row r="28">
@@ -1050,10 +1050,10 @@
         <v>-1.715451</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.319478</v>
+        <v>-0.348768</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.339848</v>
+        <v>-0.363666</v>
       </c>
     </row>
     <row r="30">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOOD.xlsx
+++ b/output/pdf_financials_xlsx/MOOD.xlsx
@@ -1218,16 +1218,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0.00252</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.002304</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.022905</v>
       </c>
     </row>
     <row r="38">
@@ -1851,16 +1849,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0.020918</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.047098</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.044235</v>
       </c>
     </row>
     <row r="65">
@@ -1920,16 +1916,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0.028</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.035394</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.04987</v>
       </c>
     </row>
     <row r="68">
